--- a/time_off_request_forms/036_religious_holiday_time_off_form--time_off_request_forms.xlsx
+++ b/time_off_request_forms/036_religious_holiday_time_off_form--time_off_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Accounting'}</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'approve'}</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Approve'}</t>
+          <t>Approve</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'deny'}</t>
+          <t>deny</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Deny'}</t>
+          <t>Deny</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'forward_to_supervisor'}</t>
+          <t>forward_to_supervisor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Forward to supervisor'}</t>
+          <t>Forward to supervisor</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'christmas'}</t>
+          <t>christmas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Christmas'}</t>
+          <t>Christmas</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_"new_year's_day"}</t>
+          <t>new_year's_day</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': "New Year's Day"}</t>
+          <t>New Year's Day</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'good_friday'}</t>
+          <t>good_friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Good Friday'}</t>
+          <t>Good Friday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'easter_monday'}</t>
+          <t>easter_monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Monday'}</t>
+          <t>Easter Monday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'easter_tuesday'}</t>
+          <t>easter_tuesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Tuesday'}</t>
+          <t>Easter Tuesday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'easter_wednesday'}</t>
+          <t>easter_wednesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Wednesday'}</t>
+          <t>Easter Wednesday</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'easter_thursday'}</t>
+          <t>easter_thursday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Thursday'}</t>
+          <t>Easter Thursday</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'easter_friday'}</t>
+          <t>easter_friday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Friday'}</t>
+          <t>Easter Friday</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'easter_saturday'}</t>
+          <t>easter_saturday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Saturday'}</t>
+          <t>Easter Saturday</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'easter_sunday'}</t>
+          <t>easter_sunday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'Easter Sunday'}</t>
+          <t>Easter Sunday</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'eid_al-fitr'}</t>
+          <t>eid_al-fitr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'Eid al-Fitr'}</t>
+          <t>Eid al-Fitr</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'eid_al-adha'}</t>
+          <t>eid_al-adha</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'Eid al-Adha'}</t>
+          <t>Eid al-Adha</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'diwali'}</t>
+          <t>diwali</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'Diwali'}</t>
+          <t>Diwali</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'hanukkah'}</t>
+          <t>hanukkah</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'Hanukkah'}</t>
+          <t>Hanukkah</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'rosh_hashanah'}</t>
+          <t>rosh_hashanah</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'Rosh Hashanah'}</t>
+          <t>Rosh Hashanah</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'sukkot'}</t>
+          <t>sukkot</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'Sukkot'}</t>
+          <t>Sukkot</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'thanksgiving_day'}</t>
+          <t>thanksgiving_day</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'Thanksgiving Day'}</t>
+          <t>Thanksgiving Day</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'thanksgiving_night'}</t>
+          <t>thanksgiving_night</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'Thanksgiving Night'}</t>
+          <t>Thanksgiving Night</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'christmas_day'}</t>
+          <t>christmas_day</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'Christmas Day'}</t>
+          <t>Christmas Day</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'christmas_night'}</t>
+          <t>christmas_night</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'Christmas Night'}</t>
+          <t>Christmas Night</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_"new_year's_day_eve"}</t>
+          <t>new_year's_day_eve</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': "New Year's Day Eve"}</t>
+          <t>New Year's Day Eve</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_"new_year's_day_morning"}</t>
+          <t>new_year's_day_morning</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': "New Year's Day Morning"}</t>
+          <t>New Year's Day Morning</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz'}</t>
+          <t>nowruz</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz'}</t>
+          <t>Nowruz</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'name':_'chinese_new_year'}</t>
+          <t>chinese_new_year</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'name': 'Chinese New Year'}</t>
+          <t>Chinese New Year</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'name':_"chinese_new_year's_eve"}</t>
+          <t>chinese_new_year's_eve</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'name': "Chinese New Year's Eve"}</t>
+          <t>Chinese New Year's Eve</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'name':_"chinese_new_year's_morning"}</t>
+          <t>chinese_new_year's_morning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'name': "Chinese New Year's Morning"}</t>
+          <t>Chinese New Year's Morning</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_day'}</t>
+          <t>nowruz_day</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Day'}</t>
+          <t>Nowruz Day</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_night'}</t>
+          <t>nowruz_night</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Night'}</t>
+          <t>Nowruz Night</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_morning'}</t>
+          <t>nowruz_morning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Morning'}</t>
+          <t>Nowruz Morning</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_evening'}</t>
+          <t>nowruz_evening</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Evening'}</t>
+          <t>Nowruz Evening</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_afternoon'}</t>
+          <t>nowruz_afternoon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Afternoon'}</t>
+          <t>Nowruz Afternoon</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_afternoon'}</t>
+          <t>hanukkah_day</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Afternoon'}</t>
+          <t>Hanukkah Day</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'name':_'nowruz_afternoon'}</t>
+          <t>hanukkah_night</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'name': 'Nowruz Afternoon'}</t>
+          <t>Hanukkah Night</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'name':_'hanukkah_day'}</t>
+          <t>hanukkah_morning</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'name': 'Hanukkah Day'}</t>
+          <t>Hanukkah Morning</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'name':_'hanukkah_night'}</t>
+          <t>hanukkah_evening</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'name': 'Hanukkah Night'}</t>
+          <t>Hanukkah Evening</t>
         </is>
       </c>
     </row>
@@ -1879,63 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'name':_'hanukkah_morning'}</t>
+          <t>hanukkah_afternoon</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'name': 'Hanukkah Morning'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>religious_holiday_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'name':_'hanukkah_evening'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'name': 'Hanukkah Evening'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>religious_holiday_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'name':_'hanukkah_afternoon'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'name': 'Hanukkah Afternoon'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>religious_holiday_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'name':_'hanukkah_afternoon'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'name': 'Hanukkah Afternoon'}</t>
+          <t>Hanukkah Afternoon</t>
         </is>
       </c>
     </row>
